--- a/app/data/grasslands-cases.xlsx
+++ b/app/data/grasslands-cases.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M Walker</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>E Carter</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>A Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>R Singh</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>J Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>L Owusu</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>T Okafor</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>P Shah</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,11 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -878,7 +882,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>M Walker</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -918,7 +922,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>E Carter</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -958,7 +962,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>A Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -998,7 +1002,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>R Singh</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1042,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>J Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>L Owusu</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2002,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>E Carter</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2042,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>A Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2082,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>R Singh</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>J Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2162,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>L Owusu</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2202,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>T Okafor</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2242,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P Shah</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2282,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>K Reed</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2322,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>M Walker</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2362,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>E Carter</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2402,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>A Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>R Singh</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2482,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>J Jones</t>
+          <t>Not assigned</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3395,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3427,7 +3435,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3463,7 +3475,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3499,7 +3515,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3535,7 +3555,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3571,7 +3595,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3607,7 +3635,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3643,7 +3675,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3679,7 +3715,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3715,7 +3755,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3751,7 +3795,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3787,7 +3835,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
@@ -3823,7 +3875,11 @@
           <t>grey</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Not assigned</t>
